--- a/student_results.xlsx
+++ b/student_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,51 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>nandini</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3rd year</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>96</v>
+      </c>
+      <c r="E2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2" t="n">
+        <v>88</v>
+      </c>
+      <c r="G2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I2" t="n">
+        <v>444</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>88.8%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
